--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junse\PycharmProjects\리액\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D19A807-3C2E-4C16-850A-3DE4EAF955EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B0F0835-5E66-4CEF-AD8F-07FC9CB941EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="11244" windowHeight="8808" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$D$1:$D$1348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="919">
   <si>
     <t>송인욱</t>
   </si>
@@ -2896,9 +2896,6 @@
     <t>제 11회 워크샵 공연 - &lt;지상 최후의 농담&gt;</t>
   </si>
   <si>
-    <t>제 10회 워크샵 공연</t>
-  </si>
-  <si>
     <t>제 12회 워크샵 공연 - &lt;투명영웅&gt;</t>
   </si>
   <si>
@@ -2915,15 +2912,6 @@
   </si>
   <si>
     <t>제 14회 워크샵 공연 - &lt;사람을 죽이지 않는 법&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">제 25회 정기공연 〈나무는 서서 죽는다〉  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">제 24회 정기공연 〈밤산책〉  </t>
-  </si>
-  <si>
-    <t>OB공연 〈시라노〉</t>
   </si>
   <si>
     <t>리버액트 2기</t>
@@ -3618,32 +3606,30 @@
         <v>166</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2">
-        <v>2013</v>
-      </c>
-      <c r="C2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" t="s">
-        <v>806</v>
-      </c>
-      <c r="E2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>428</v>
-      </c>
+      <c r="A2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2024</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B3">
         <v>2013</v>
@@ -3655,12 +3641,15 @@
         <v>806</v>
       </c>
       <c r="E3" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>101</v>
+      <c r="A4" t="s">
+        <v>110</v>
       </c>
       <c r="B4">
         <v>2013</v>
@@ -3672,49 +3661,49 @@
         <v>806</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" t="s">
-        <v>438</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5">
+        <v>2013</v>
+      </c>
+      <c r="C5" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" t="s">
+        <v>806</v>
+      </c>
+      <c r="E5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="1">
         <v>2014</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>148</v>
-      </c>
-      <c r="B6">
-        <v>2014</v>
-      </c>
-      <c r="C6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" t="s">
-        <v>804</v>
-      </c>
-      <c r="E6" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>2014</v>
@@ -3726,15 +3715,12 @@
         <v>804</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F7" t="s">
-        <v>461</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B8">
         <v>2014</v>
@@ -3749,29 +3735,32 @@
         <v>111</v>
       </c>
       <c r="F8" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C9" t="s">
         <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="F9" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="B10">
         <v>2015</v>
@@ -3788,7 +3777,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B11">
         <v>2015</v>
@@ -3800,15 +3789,12 @@
         <v>824</v>
       </c>
       <c r="E11" t="s">
-        <v>111</v>
-      </c>
-      <c r="F11" t="s">
-        <v>457</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="B12">
         <v>2015</v>
@@ -3823,12 +3809,12 @@
         <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="B13">
         <v>2015</v>
@@ -3843,7 +3829,7 @@
         <v>111</v>
       </c>
       <c r="F13" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
@@ -3851,21 +3837,24 @@
         <v>77</v>
       </c>
       <c r="B14">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C14" t="s">
         <v>189</v>
       </c>
       <c r="D14" t="s">
-        <v>846</v>
+        <v>824</v>
       </c>
       <c r="E14" t="s">
-        <v>159</v>
+        <v>111</v>
+      </c>
+      <c r="F14" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>50</v>
+      <c r="A15" t="s">
+        <v>77</v>
       </c>
       <c r="B15">
         <v>2016</v>
@@ -3877,15 +3866,12 @@
         <v>846</v>
       </c>
       <c r="E15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" t="s">
-        <v>516</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>2016</v>
@@ -3896,33 +3882,36 @@
       <c r="D16" t="s">
         <v>846</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>483</v>
+      <c r="E16" t="s">
+        <v>111</v>
       </c>
       <c r="F16" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>131</v>
+      <c r="A17" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C17" t="s">
         <v>189</v>
       </c>
       <c r="D17" t="s">
-        <v>817</v>
-      </c>
-      <c r="E17" t="s">
-        <v>159</v>
+        <v>846</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F17" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="B18">
         <v>2017</v>
@@ -3934,15 +3923,12 @@
         <v>817</v>
       </c>
       <c r="E18" t="s">
-        <v>111</v>
-      </c>
-      <c r="F18" t="s">
-        <v>496</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>32</v>
+      <c r="A19" t="s">
+        <v>53</v>
       </c>
       <c r="B19">
         <v>2017</v>
@@ -3957,29 +3943,32 @@
         <v>111</v>
       </c>
       <c r="F19" t="s">
-        <v>525</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C20" t="s">
         <v>189</v>
       </c>
       <c r="D20" t="s">
-        <v>855</v>
+        <v>817</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B21">
         <v>2018</v>
@@ -3990,16 +3979,13 @@
       <c r="D21" t="s">
         <v>855</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F21" t="s">
-        <v>114</v>
+      <c r="E21" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B22">
         <v>2018</v>
@@ -4010,33 +3996,33 @@
       <c r="D22" t="s">
         <v>855</v>
       </c>
-      <c r="E22" t="s">
-        <v>159</v>
+      <c r="E22" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F22" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" t="s">
-        <v>15</v>
+      <c r="A23" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C23" t="s">
         <v>189</v>
       </c>
       <c r="D23" t="s">
-        <v>861</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F23" t="s">
-        <v>562</v>
+        <v>855</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24">
         <v>2019</v>
@@ -4047,13 +4033,16 @@
       <c r="D24" t="s">
         <v>861</v>
       </c>
-      <c r="E24" t="s">
-        <v>159</v>
+      <c r="E24" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F24" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="3" t="s">
-        <v>249</v>
+      <c r="A25" t="s">
+        <v>16</v>
       </c>
       <c r="B25">
         <v>2019</v>
@@ -4065,32 +4054,32 @@
         <v>861</v>
       </c>
       <c r="E25" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" t="s">
-        <v>580</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>58</v>
+      <c r="A26" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="B26">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C26" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="D26" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="E26" t="s">
         <v>111</v>
       </c>
+      <c r="F26" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="3" t="s">
-        <v>268</v>
+      <c r="A27" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="B27">
         <v>2020</v>
@@ -4102,12 +4091,12 @@
         <v>856</v>
       </c>
       <c r="E27" t="s">
-        <v>256</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="B28">
         <v>2020</v>
@@ -4118,36 +4107,33 @@
       <c r="D28" t="s">
         <v>856</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F28" t="s">
-        <v>111</v>
+      <c r="E28" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B29">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C29" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
-        <v>883</v>
+        <v>856</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>785</v>
+        <v>483</v>
+      </c>
+      <c r="F29" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="B30">
         <v>2022</v>
@@ -4159,35 +4145,35 @@
         <v>883</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F30" t="s">
-        <v>653</v>
+        <v>770</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="3" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="B31">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C31" t="s">
         <v>189</v>
       </c>
       <c r="D31" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>483</v>
       </c>
       <c r="F31" t="s">
-        <v>629</v>
+        <v>653</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="3" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="B32">
         <v>2024</v>
@@ -4198,13 +4184,16 @@
       <c r="D32" t="s">
         <v>886</v>
       </c>
-      <c r="E32" t="s">
-        <v>159</v>
+      <c r="E32" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F32" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="3" t="s">
-        <v>369</v>
+        <v>314</v>
       </c>
       <c r="B33">
         <v>2024</v>
@@ -4215,16 +4204,13 @@
       <c r="D33" t="s">
         <v>886</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F33" t="s">
-        <v>693</v>
+      <c r="E33" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B34">
         <v>2024</v>
@@ -4239,32 +4225,32 @@
         <v>483</v>
       </c>
       <c r="F34" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="3" t="s">
-        <v>300</v>
+        <v>366</v>
       </c>
       <c r="B35">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C35" t="s">
         <v>189</v>
       </c>
       <c r="D35" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>483</v>
       </c>
       <c r="F35" t="s">
-        <v>630</v>
+        <v>687</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="3" t="s">
-        <v>365</v>
+        <v>300</v>
       </c>
       <c r="B36">
         <v>2025</v>
@@ -4279,12 +4265,12 @@
         <v>483</v>
       </c>
       <c r="F36" t="s">
-        <v>686</v>
+        <v>630</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B37">
         <v>2025</v>
@@ -4295,50 +4281,50 @@
       <c r="D37" t="s">
         <v>887</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F37" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B38">
+        <v>2025</v>
+      </c>
+      <c r="C38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>887</v>
+      </c>
+      <c r="E38" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A39" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B39" s="1">
         <v>2026</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A39" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
         <v>135</v>
-      </c>
-      <c r="B39">
-        <v>2026</v>
-      </c>
-      <c r="C39" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F39" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="3" t="s">
-        <v>397</v>
       </c>
       <c r="B40">
         <v>2026</v>
@@ -4349,13 +4335,16 @@
       <c r="D40" t="s">
         <v>27</v>
       </c>
-      <c r="E40" t="s">
-        <v>84</v>
+      <c r="E40" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F40" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B41">
         <v>2026</v>
@@ -4366,55 +4355,55 @@
       <c r="D41" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A42" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B42">
+        <v>2026</v>
+      </c>
+      <c r="C42" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A43" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2025</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F42" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A43" t="s">
-        <v>142</v>
       </c>
       <c r="B43" s="1">
         <v>2025</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E43" t="s">
-        <v>193</v>
+      <c r="E43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F43" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>133</v>
-      </c>
-      <c r="B44">
+        <v>142</v>
+      </c>
+      <c r="B44" s="1">
         <v>2025</v>
       </c>
       <c r="C44" t="s">
@@ -4424,15 +4413,12 @@
         <v>233</v>
       </c>
       <c r="E44" t="s">
-        <v>111</v>
-      </c>
-      <c r="F44" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="B45">
         <v>2025</v>
@@ -4444,15 +4430,15 @@
         <v>233</v>
       </c>
       <c r="E45" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>433</v>
+        <v>111</v>
+      </c>
+      <c r="F45" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A46" s="1" t="s">
-        <v>75</v>
+      <c r="A46" t="s">
+        <v>53</v>
       </c>
       <c r="B46">
         <v>2025</v>
@@ -4463,16 +4449,16 @@
       <c r="D46" t="s">
         <v>233</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F46" t="s">
-        <v>541</v>
+      <c r="E46" t="s">
+        <v>195</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A47" t="s">
-        <v>15</v>
+      <c r="A47" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="B47">
         <v>2025</v>
@@ -4483,16 +4469,16 @@
       <c r="D47" t="s">
         <v>233</v>
       </c>
-      <c r="E47" t="s">
-        <v>144</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>433</v>
+      <c r="E47" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F47" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B48">
         <v>2025</v>
@@ -4503,16 +4489,16 @@
       <c r="D48" t="s">
         <v>233</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F48" t="s">
-        <v>564</v>
+      <c r="E48" t="s">
+        <v>144</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A49" s="3" t="s">
-        <v>261</v>
+      <c r="A49" t="s">
+        <v>16</v>
       </c>
       <c r="B49">
         <v>2025</v>
@@ -4523,13 +4509,16 @@
       <c r="D49" t="s">
         <v>233</v>
       </c>
-      <c r="E49" t="s">
-        <v>253</v>
+      <c r="E49" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F49" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="3" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B50">
         <v>2025</v>
@@ -4541,15 +4530,12 @@
         <v>233</v>
       </c>
       <c r="E50" t="s">
-        <v>255</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>433</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B51">
         <v>2025</v>
@@ -4560,16 +4546,16 @@
       <c r="D51" t="s">
         <v>233</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F51" t="s">
-        <v>616</v>
+      <c r="E51" t="s">
+        <v>255</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B52">
         <v>2025</v>
@@ -4580,16 +4566,16 @@
       <c r="D52" t="s">
         <v>233</v>
       </c>
-      <c r="E52" t="s">
-        <v>96</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>433</v>
+      <c r="E52" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F52" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="3" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="B53">
         <v>2025</v>
@@ -4601,12 +4587,15 @@
         <v>233</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="3" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="B54">
         <v>2025</v>
@@ -4618,12 +4607,12 @@
         <v>233</v>
       </c>
       <c r="E54" t="s">
-        <v>329</v>
+        <v>132</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="3" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B55">
         <v>2025</v>
@@ -4635,12 +4624,12 @@
         <v>233</v>
       </c>
       <c r="E55" t="s">
-        <v>89</v>
+        <v>329</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B56">
         <v>2025</v>
@@ -4652,12 +4641,12 @@
         <v>233</v>
       </c>
       <c r="E56" t="s">
-        <v>329</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="3" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B57">
         <v>2025</v>
@@ -4668,16 +4657,13 @@
       <c r="D57" t="s">
         <v>233</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F57" t="s">
-        <v>677</v>
+      <c r="E57" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B58">
         <v>2025</v>
@@ -4688,13 +4674,16 @@
       <c r="D58" t="s">
         <v>233</v>
       </c>
-      <c r="E58" t="s">
-        <v>79</v>
+      <c r="E58" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F58" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B59">
         <v>2025</v>
@@ -4711,7 +4700,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B60">
         <v>2025</v>
@@ -4723,12 +4712,12 @@
         <v>233</v>
       </c>
       <c r="E60" t="s">
-        <v>329</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B61">
         <v>2025</v>
@@ -4740,12 +4729,12 @@
         <v>233</v>
       </c>
       <c r="E61" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="3" t="s">
-        <v>397</v>
+        <v>366</v>
       </c>
       <c r="B62">
         <v>2025</v>
@@ -4756,16 +4745,13 @@
       <c r="D62" t="s">
         <v>233</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F62" t="s">
-        <v>719</v>
+      <c r="E62" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="3" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="B63">
         <v>2025</v>
@@ -4780,54 +4766,54 @@
         <v>483</v>
       </c>
       <c r="F63" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A64" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B64">
+        <v>2025</v>
+      </c>
+      <c r="C64" t="s">
+        <v>198</v>
+      </c>
+      <c r="D64" t="s">
+        <v>233</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F64" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A64" s="1" t="s">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A65" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B64" s="1">
-        <v>2024</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F64" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A65" t="s">
-        <v>142</v>
       </c>
       <c r="B65" s="1">
         <v>2024</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>111</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A66" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B66">
+      <c r="A66" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="1">
         <v>2024</v>
       </c>
       <c r="C66" t="s">
@@ -4836,16 +4822,16 @@
       <c r="D66" t="s">
         <v>29</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>483</v>
+      <c r="E66" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="F66" t="s">
-        <v>540</v>
+        <v>113</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A67" s="3" t="s">
-        <v>287</v>
+      <c r="A67" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="B67">
         <v>2024</v>
@@ -4860,12 +4846,12 @@
         <v>483</v>
       </c>
       <c r="F67" t="s">
-        <v>602</v>
+        <v>540</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="3" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B68">
         <v>2024</v>
@@ -4880,12 +4866,12 @@
         <v>483</v>
       </c>
       <c r="F68" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
-        <v>312</v>
+        <v>278</v>
       </c>
       <c r="B69">
         <v>2024</v>
@@ -4900,12 +4886,12 @@
         <v>483</v>
       </c>
       <c r="F69" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="B70">
         <v>2024</v>
@@ -4916,16 +4902,16 @@
       <c r="D70" t="s">
         <v>29</v>
       </c>
-      <c r="E70" t="s">
-        <v>96</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>433</v>
+      <c r="E70" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F70" t="s">
+        <v>646</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71" s="3" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="B71">
         <v>2024</v>
@@ -4937,12 +4923,15 @@
         <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B72">
         <v>2024</v>
@@ -4954,15 +4943,12 @@
         <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>200</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>433</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="3" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="B73">
         <v>2024</v>
@@ -4974,74 +4960,74 @@
         <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>89</v>
+        <v>200</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" s="3" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="B74">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C74" t="s">
         <v>198</v>
       </c>
       <c r="D74" t="s">
-        <v>898</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F74" t="s">
-        <v>603</v>
+        <v>29</v>
+      </c>
+      <c r="E74" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A75" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B75" s="1">
+      <c r="A75" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B75">
         <v>2025</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" t="s">
         <v>198</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>111</v>
+      <c r="E75" s="3" t="s">
+        <v>483</v>
       </c>
       <c r="F75" t="s">
-        <v>203</v>
+        <v>603</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A76" t="s">
-        <v>142</v>
+      <c r="A76" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="B76" s="1">
         <v>2025</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E76" t="s">
-        <v>144</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>433</v>
+      <c r="E76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F76" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>133</v>
-      </c>
-      <c r="B77">
+        <v>142</v>
+      </c>
+      <c r="B77" s="1">
         <v>2025</v>
       </c>
       <c r="C77" t="s">
@@ -5051,15 +5037,15 @@
         <v>224</v>
       </c>
       <c r="E77" t="s">
-        <v>111</v>
-      </c>
-      <c r="F77" t="s">
-        <v>24</v>
+        <v>144</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="B78">
         <v>2025</v>
@@ -5071,14 +5057,17 @@
         <v>224</v>
       </c>
       <c r="E78" t="s">
-        <v>89</v>
+        <v>111</v>
+      </c>
+      <c r="F78" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>53</v>
-      </c>
-      <c r="B79" s="1">
+        <v>76</v>
+      </c>
+      <c r="B79">
         <v>2025</v>
       </c>
       <c r="C79" t="s">
@@ -5088,17 +5077,14 @@
         <v>224</v>
       </c>
       <c r="E79" t="s">
-        <v>96</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>433</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A80" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B80">
+      <c r="A80" t="s">
+        <v>53</v>
+      </c>
+      <c r="B80" s="1">
         <v>2025</v>
       </c>
       <c r="C80" t="s">
@@ -5108,12 +5094,15 @@
         <v>224</v>
       </c>
       <c r="E80" t="s">
-        <v>109</v>
+        <v>96</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A81" t="s">
-        <v>16</v>
+      <c r="A81" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="B81">
         <v>2025</v>
@@ -5125,12 +5114,12 @@
         <v>224</v>
       </c>
       <c r="E81" t="s">
-        <v>3</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A82" s="3" t="s">
-        <v>259</v>
+      <c r="A82" t="s">
+        <v>16</v>
       </c>
       <c r="B82">
         <v>2025</v>
@@ -5141,19 +5130,13 @@
       <c r="D82" t="s">
         <v>224</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>433</v>
+      <c r="E82" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A83" s="3" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B83">
         <v>2025</v>
@@ -5164,13 +5147,19 @@
       <c r="D83" t="s">
         <v>224</v>
       </c>
-      <c r="E83" t="s">
-        <v>3</v>
+      <c r="E83" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A84" s="3" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B84">
         <v>2025</v>
@@ -5182,12 +5171,12 @@
         <v>224</v>
       </c>
       <c r="E84" t="s">
-        <v>168</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A85" s="3" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="B85">
         <v>2025</v>
@@ -5199,12 +5188,12 @@
         <v>224</v>
       </c>
       <c r="E85" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A86" s="3" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="B86">
         <v>2025</v>
@@ -5216,12 +5205,12 @@
         <v>224</v>
       </c>
       <c r="E86" t="s">
-        <v>325</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A87" s="3" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="B87">
         <v>2025</v>
@@ -5232,16 +5221,13 @@
       <c r="D87" t="s">
         <v>224</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F87" t="s">
-        <v>612</v>
+      <c r="E87" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A88" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B88">
         <v>2025</v>
@@ -5252,13 +5238,16 @@
       <c r="D88" t="s">
         <v>224</v>
       </c>
-      <c r="E88" t="s">
-        <v>79</v>
+      <c r="E88" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F88" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A89" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B89">
         <v>2025</v>
@@ -5275,7 +5264,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A90" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B90">
         <v>2025</v>
@@ -5287,15 +5276,12 @@
         <v>224</v>
       </c>
       <c r="E90" t="s">
-        <v>96</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>433</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A91" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B91">
         <v>2025</v>
@@ -5307,12 +5293,15 @@
         <v>224</v>
       </c>
       <c r="E91" t="s">
-        <v>3</v>
+        <v>96</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A92" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B92">
         <v>2025</v>
@@ -5323,16 +5312,13 @@
       <c r="D92" t="s">
         <v>224</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F92" t="s">
-        <v>595</v>
+      <c r="E92" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A93" s="3" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="B93">
         <v>2025</v>
@@ -5343,13 +5329,16 @@
       <c r="D93" t="s">
         <v>224</v>
       </c>
-      <c r="E93" t="s">
-        <v>380</v>
+      <c r="E93" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F93" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A94" s="3" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B94">
         <v>2025</v>
@@ -5360,36 +5349,33 @@
       <c r="D94" t="s">
         <v>224</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E94" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A95" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B95">
+        <v>2025</v>
+      </c>
+      <c r="C95" t="s">
+        <v>198</v>
+      </c>
+      <c r="D95" t="s">
+        <v>224</v>
+      </c>
+      <c r="E95" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F95" t="s">
         <v>567</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A95" t="s">
-        <v>88</v>
-      </c>
-      <c r="B95">
-        <v>2020</v>
-      </c>
-      <c r="C95" t="s">
-        <v>213</v>
-      </c>
-      <c r="D95" t="s">
-        <v>814</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B96">
         <v>2020</v>
@@ -5401,15 +5387,15 @@
         <v>814</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B97">
         <v>2020</v>
@@ -5420,13 +5406,16 @@
       <c r="D97" t="s">
         <v>814</v>
       </c>
-      <c r="E97" t="s">
-        <v>228</v>
+      <c r="E97" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="B98">
         <v>2020</v>
@@ -5437,16 +5426,13 @@
       <c r="D98" t="s">
         <v>814</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>754</v>
+      <c r="E98" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="B99">
         <v>2020</v>
@@ -5458,15 +5444,15 @@
         <v>814</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B100">
         <v>2020</v>
@@ -5478,15 +5464,15 @@
         <v>814</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B101">
         <v>2020</v>
@@ -5497,16 +5483,16 @@
       <c r="D101" t="s">
         <v>814</v>
       </c>
-      <c r="E101" t="s">
-        <v>207</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>433</v>
+      <c r="E101" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A102" s="1" t="s">
-        <v>37</v>
+      <c r="A102" t="s">
+        <v>53</v>
       </c>
       <c r="B102">
         <v>2020</v>
@@ -5518,12 +5504,15 @@
         <v>814</v>
       </c>
       <c r="E102" t="s">
-        <v>23</v>
+        <v>207</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A103" s="1" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B103">
         <v>2020</v>
@@ -5534,16 +5523,13 @@
       <c r="D103" t="s">
         <v>814</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>773</v>
+      <c r="E103" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A104" s="1" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="B104">
         <v>2020</v>
@@ -5555,15 +5541,15 @@
         <v>814</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A105" t="s">
-        <v>237</v>
+      <c r="A105" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="B105">
         <v>2020</v>
@@ -5574,13 +5560,16 @@
       <c r="D105" t="s">
         <v>814</v>
       </c>
-      <c r="E105" t="s">
-        <v>132</v>
+      <c r="E105" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>788</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A106" s="3" t="s">
-        <v>249</v>
+      <c r="A106" t="s">
+        <v>237</v>
       </c>
       <c r="B106">
         <v>2020</v>
@@ -5592,32 +5581,32 @@
         <v>814</v>
       </c>
       <c r="E106" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A107" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B107">
+        <v>2020</v>
+      </c>
+      <c r="C107" t="s">
+        <v>213</v>
+      </c>
+      <c r="D107" t="s">
+        <v>814</v>
+      </c>
+      <c r="E107" t="s">
         <v>96</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G107" s="3" t="s">
         <v>433</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A107" t="s">
-        <v>142</v>
-      </c>
-      <c r="B107">
-        <v>2026</v>
-      </c>
-      <c r="C107" t="s">
-        <v>198</v>
-      </c>
-      <c r="D107" t="s">
-        <v>225</v>
-      </c>
-      <c r="E107" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="B108">
         <v>2026</v>
@@ -5629,15 +5618,12 @@
         <v>225</v>
       </c>
       <c r="E108" t="s">
-        <v>111</v>
-      </c>
-      <c r="F108" t="s">
-        <v>497</v>
+        <v>89</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="B109">
         <v>2026</v>
@@ -5649,15 +5635,15 @@
         <v>225</v>
       </c>
       <c r="E109" t="s">
-        <v>144</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>433</v>
+        <v>111</v>
+      </c>
+      <c r="F109" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B110">
         <v>2026</v>
@@ -5669,15 +5655,15 @@
         <v>225</v>
       </c>
       <c r="E110" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A111" s="3" t="s">
-        <v>300</v>
+      <c r="A111" t="s">
+        <v>14</v>
       </c>
       <c r="B111">
         <v>2026</v>
@@ -5688,16 +5674,16 @@
       <c r="D111" t="s">
         <v>225</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="F111" t="s">
-        <v>630</v>
+      <c r="E111" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A112" s="3" t="s">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="B112">
         <v>2026</v>
@@ -5712,12 +5698,12 @@
         <v>483</v>
       </c>
       <c r="F112" t="s">
-        <v>664</v>
+        <v>630</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A113" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B113">
         <v>2026</v>
@@ -5728,13 +5714,16 @@
       <c r="D113" t="s">
         <v>225</v>
       </c>
-      <c r="E113" t="s">
-        <v>132</v>
+      <c r="E113" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="F113" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A114" s="3" t="s">
-        <v>373</v>
+        <v>345</v>
       </c>
       <c r="B114">
         <v>2026</v>
@@ -5751,7 +5740,7 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" s="3" t="s">
-        <v>407</v>
+        <v>373</v>
       </c>
       <c r="B115">
         <v>2026</v>
@@ -5763,32 +5752,32 @@
         <v>225</v>
       </c>
       <c r="E115" t="s">
-        <v>403</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>433</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A116" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B116" s="1">
-        <v>2021</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>102</v>
+        <v>407</v>
+      </c>
+      <c r="B116">
+        <v>2026</v>
+      </c>
+      <c r="C116" t="s">
+        <v>198</v>
+      </c>
+      <c r="D116" t="s">
+        <v>225</v>
+      </c>
+      <c r="E116" t="s">
+        <v>403</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A117" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B117" s="1">
         <v>2021</v>
@@ -5799,13 +5788,13 @@
       <c r="D117" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>248</v>
+      <c r="E117" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" s="3" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="B118" s="1">
         <v>2021</v>
@@ -5816,13 +5805,13 @@
       <c r="D118" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>187</v>
+      <c r="E118" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A119" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B119" s="1">
         <v>2021</v>
@@ -5839,7 +5828,7 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B120" s="1">
         <v>2021</v>
@@ -5856,7 +5845,7 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A121" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B121" s="1">
         <v>2021</v>
@@ -5873,7 +5862,7 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A122" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B122" s="1">
         <v>2021</v>
@@ -5890,7 +5879,7 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B123" s="1">
         <v>2021</v>
@@ -5907,7 +5896,7 @@
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A124" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B124" s="1">
         <v>2021</v>
@@ -5924,7 +5913,7 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B125" s="1">
         <v>2021</v>
@@ -5941,24 +5930,24 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A126" s="3" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="B126" s="1">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>179</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B127" s="1">
         <v>2022</v>
@@ -5969,13 +5958,13 @@
       <c r="D127" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>248</v>
+      <c r="E127" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A128" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B128" s="1">
         <v>2022</v>
@@ -5992,7 +5981,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A129" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B129" s="1">
         <v>2022</v>
@@ -6003,13 +5992,13 @@
       <c r="D129" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>187</v>
+      <c r="E129" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A130" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B130" s="1">
         <v>2022</v>
@@ -6026,7 +6015,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A131" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B131" s="1">
         <v>2022</v>
@@ -6043,7 +6032,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A132" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B132" s="1">
         <v>2022</v>
@@ -6060,7 +6049,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A133" s="3" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B133" s="1">
         <v>2022</v>
@@ -6077,7 +6066,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A134" s="3" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="B134" s="1">
         <v>2022</v>
@@ -6094,7 +6083,7 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A135" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B135" s="1">
         <v>2022</v>
@@ -6111,7 +6100,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A136" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B136" s="1">
         <v>2022</v>
@@ -6128,7 +6117,7 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A137" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B137" s="1">
         <v>2022</v>
@@ -6145,7 +6134,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A138" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B138" s="1">
         <v>2022</v>
@@ -6162,7 +6151,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A139" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B139" s="1">
         <v>2022</v>
@@ -6179,7 +6168,7 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A140" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B140" s="1">
         <v>2022</v>
@@ -6196,7 +6185,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A141" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B141" s="1">
         <v>2022</v>
@@ -6213,7 +6202,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A142" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B142" s="1">
         <v>2022</v>
@@ -6230,7 +6219,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A143" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B143" s="1">
         <v>2022</v>
@@ -6247,7 +6236,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A144" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B144" s="1">
         <v>2022</v>
@@ -6264,7 +6253,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A145" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B145" s="1">
         <v>2022</v>
@@ -6281,7 +6270,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A146" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B146" s="1">
         <v>2022</v>
@@ -6297,17 +6286,17 @@
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A147" t="s">
-        <v>95</v>
-      </c>
-      <c r="B147">
-        <v>2023</v>
+      <c r="A147" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B147" s="1">
+        <v>2022</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D147" s="1" t="s">
-        <v>217</v>
+      <c r="D147" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>187</v>
@@ -6315,7 +6304,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="B148">
         <v>2023</v>
@@ -6331,25 +6320,25 @@
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A149" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="B149" s="1">
+      <c r="A149" t="s">
+        <v>142</v>
+      </c>
+      <c r="B149">
         <v>2023</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D149" s="2" t="s">
-        <v>326</v>
+      <c r="D149" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A150" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B150" s="1">
         <v>2023</v>
@@ -6360,13 +6349,13 @@
       <c r="D150" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>248</v>
+      <c r="E150" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A151" s="3" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="B151" s="1">
         <v>2023</v>
@@ -6377,13 +6366,13 @@
       <c r="D151" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>187</v>
+      <c r="E151" s="2" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A152" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B152" s="1">
         <v>2023</v>
@@ -6400,7 +6389,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A153" s="3" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="B153" s="1">
         <v>2023</v>
@@ -6417,7 +6406,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A154" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B154" s="1">
         <v>2023</v>
@@ -6434,7 +6423,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A155" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B155" s="1">
         <v>2023</v>
@@ -6451,7 +6440,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A156" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B156" s="1">
         <v>2023</v>
@@ -6468,7 +6457,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A157" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B157" s="1">
         <v>2023</v>
@@ -6485,7 +6474,7 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A158" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B158" s="1">
         <v>2023</v>
@@ -6502,7 +6491,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A159" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B159" s="1">
         <v>2023</v>
@@ -6519,7 +6508,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A160" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B160" s="1">
         <v>2023</v>
@@ -6536,7 +6525,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A161" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B161" s="1">
         <v>2023</v>
@@ -6553,7 +6542,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A162" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B162" s="1">
         <v>2023</v>
@@ -6570,7 +6559,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A163" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B163" s="1">
         <v>2023</v>
@@ -6587,7 +6576,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A164" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B164" s="1">
         <v>2023</v>
@@ -6604,7 +6593,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A165" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B165" s="1">
         <v>2023</v>
@@ -6621,7 +6610,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A166" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B166" s="1">
         <v>2023</v>
@@ -6638,7 +6627,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A167" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B167" s="1">
         <v>2023</v>
@@ -6655,7 +6644,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A168" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B168" s="1">
         <v>2023</v>
@@ -6672,7 +6661,7 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A169" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B169" s="1">
         <v>2023</v>
@@ -6689,7 +6678,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A170" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B170" s="1">
         <v>2023</v>
@@ -6705,20 +6694,20 @@
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A171" s="1" t="s">
-        <v>95</v>
+      <c r="A171" s="3" t="s">
+        <v>376</v>
       </c>
       <c r="B171" s="1">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>216</v>
+      <c r="D171" s="2" t="s">
+        <v>326</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.4">
@@ -8113,7 +8102,7 @@
         <v>179</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E253" s="1" t="s">
         <v>187</v>
@@ -10719,7 +10708,7 @@
         <v>92</v>
       </c>
       <c r="D404" t="s">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="E404" t="s">
         <v>273</v>
@@ -11545,7 +11534,7 @@
         <v>92</v>
       </c>
       <c r="D448" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E448" t="s">
         <v>84</v>
@@ -11562,7 +11551,7 @@
         <v>92</v>
       </c>
       <c r="D449" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E449" t="s">
         <v>84</v>
@@ -11579,7 +11568,7 @@
         <v>92</v>
       </c>
       <c r="D450" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E450" t="s">
         <v>84</v>
@@ -11596,7 +11585,7 @@
         <v>92</v>
       </c>
       <c r="D451" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E451" t="s">
         <v>84</v>
@@ -11613,7 +11602,7 @@
         <v>92</v>
       </c>
       <c r="D452" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E452" t="s">
         <v>84</v>
@@ -12534,7 +12523,7 @@
         <v>92</v>
       </c>
       <c r="D500" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E500" t="s">
         <v>324</v>
@@ -12551,7 +12540,7 @@
         <v>92</v>
       </c>
       <c r="D501" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E501" t="s">
         <v>328</v>
@@ -12568,7 +12557,7 @@
         <v>92</v>
       </c>
       <c r="D502" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E502" t="s">
         <v>324</v>
@@ -12585,7 +12574,7 @@
         <v>92</v>
       </c>
       <c r="D503" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E503" t="s">
         <v>328</v>
@@ -12602,7 +12591,7 @@
         <v>92</v>
       </c>
       <c r="D504" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E504" t="s">
         <v>324</v>
@@ -12619,7 +12608,7 @@
         <v>92</v>
       </c>
       <c r="D505" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E505" t="s">
         <v>357</v>
@@ -12693,7 +12682,7 @@
         <v>92</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>159</v>
@@ -12710,7 +12699,7 @@
         <v>92</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E510" s="3" t="s">
         <v>483</v>
@@ -12730,7 +12719,7 @@
         <v>92</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E511" s="3" t="s">
         <v>483</v>
@@ -12750,7 +12739,7 @@
         <v>92</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E512" s="3" t="s">
         <v>483</v>
@@ -12770,7 +12759,7 @@
         <v>92</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="E513" s="3" t="s">
         <v>483</v>
@@ -12790,7 +12779,7 @@
         <v>92</v>
       </c>
       <c r="D514" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E514" s="3" t="s">
         <v>483</v>
@@ -12810,7 +12799,7 @@
         <v>92</v>
       </c>
       <c r="D515" s="3" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="E515" s="3" t="s">
         <v>483</v>
@@ -12830,7 +12819,7 @@
         <v>92</v>
       </c>
       <c r="D516" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E516" t="s">
         <v>159</v>
@@ -12847,7 +12836,7 @@
         <v>92</v>
       </c>
       <c r="D517" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.4">
@@ -12861,7 +12850,7 @@
         <v>92</v>
       </c>
       <c r="D518" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E518" s="3" t="s">
         <v>483</v>
@@ -12881,7 +12870,7 @@
         <v>92</v>
       </c>
       <c r="D519" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E519" s="3" t="s">
         <v>483</v>
@@ -12901,7 +12890,7 @@
         <v>92</v>
       </c>
       <c r="D520" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E520" t="s">
         <v>200</v>
@@ -12918,7 +12907,7 @@
         <v>92</v>
       </c>
       <c r="D521" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E521" s="3" t="s">
         <v>483</v>
@@ -12938,7 +12927,7 @@
         <v>92</v>
       </c>
       <c r="D522" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E522" t="s">
         <v>159</v>
@@ -12955,7 +12944,7 @@
         <v>92</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E523" s="3" t="s">
         <v>483</v>
@@ -12975,7 +12964,7 @@
         <v>92</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E524" s="3" t="s">
         <v>483</v>
@@ -12995,7 +12984,7 @@
         <v>92</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E525" s="3" t="s">
         <v>483</v>
@@ -13015,7 +13004,7 @@
         <v>92</v>
       </c>
       <c r="D526" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E526" s="3" t="s">
         <v>483</v>
@@ -13035,7 +13024,7 @@
         <v>92</v>
       </c>
       <c r="D527" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E527" s="3" t="s">
         <v>483</v>
@@ -13055,7 +13044,7 @@
         <v>92</v>
       </c>
       <c r="D528" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E528" s="3" t="s">
         <v>780</v>
@@ -13553,7 +13542,7 @@
         <v>92</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>200</v>
@@ -13570,7 +13559,7 @@
         <v>92</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E556" s="3" t="s">
         <v>483</v>
@@ -13590,7 +13579,7 @@
         <v>92</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E557" s="3" t="s">
         <v>483</v>
@@ -13610,7 +13599,7 @@
         <v>92</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="E558" s="3" t="s">
         <v>483</v>
@@ -13630,7 +13619,7 @@
         <v>92</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E559" s="3" t="s">
         <v>483</v>
@@ -13650,7 +13639,7 @@
         <v>92</v>
       </c>
       <c r="D560" s="3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E560" s="3" t="s">
         <v>483</v>
@@ -13670,7 +13659,7 @@
         <v>92</v>
       </c>
       <c r="D561" s="3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="E561" t="s">
         <v>200</v>
@@ -13687,7 +13676,7 @@
         <v>92</v>
       </c>
       <c r="D562" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E562" s="3" t="s">
         <v>770</v>
@@ -13707,7 +13696,7 @@
         <v>92</v>
       </c>
       <c r="D563" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E563" s="3" t="s">
         <v>483</v>
@@ -13727,7 +13716,7 @@
         <v>92</v>
       </c>
       <c r="D564" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E564" s="3" t="s">
         <v>483</v>
@@ -13747,7 +13736,7 @@
         <v>92</v>
       </c>
       <c r="D565" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E565" s="3" t="s">
         <v>483</v>
@@ -13767,7 +13756,7 @@
         <v>92</v>
       </c>
       <c r="D566" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E566" s="3" t="s">
         <v>483</v>
@@ -13787,7 +13776,7 @@
         <v>92</v>
       </c>
       <c r="D567" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.4">
@@ -13801,7 +13790,7 @@
         <v>92</v>
       </c>
       <c r="D568" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="E568" s="3" t="s">
         <v>483</v>
@@ -13821,7 +13810,7 @@
         <v>92</v>
       </c>
       <c r="D569" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="E569" s="3" t="s">
         <v>483</v>
@@ -13841,7 +13830,7 @@
         <v>92</v>
       </c>
       <c r="D570" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="E570" s="3" t="s">
         <v>483</v>
@@ -13861,7 +13850,7 @@
         <v>92</v>
       </c>
       <c r="D571" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="E571" s="3" t="s">
         <v>483</v>
@@ -13881,7 +13870,7 @@
         <v>92</v>
       </c>
       <c r="D572" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>111</v>
@@ -13901,7 +13890,7 @@
         <v>92</v>
       </c>
       <c r="D573" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E573" t="s">
         <v>111</v>
@@ -13921,7 +13910,7 @@
         <v>92</v>
       </c>
       <c r="D574" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E574" t="s">
         <v>200</v>
@@ -13938,7 +13927,7 @@
         <v>92</v>
       </c>
       <c r="D575" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E575" s="3" t="s">
         <v>483</v>
@@ -13958,7 +13947,7 @@
         <v>92</v>
       </c>
       <c r="D576" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E576" s="3" t="s">
         <v>483</v>
@@ -13978,7 +13967,7 @@
         <v>92</v>
       </c>
       <c r="D577" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="E577" s="3" t="s">
         <v>483</v>
@@ -13998,7 +13987,7 @@
         <v>92</v>
       </c>
       <c r="D578" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>111</v>
@@ -14018,7 +14007,7 @@
         <v>92</v>
       </c>
       <c r="D579" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E579" t="s">
         <v>111</v>
@@ -14038,7 +14027,7 @@
         <v>92</v>
       </c>
       <c r="D580" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E580" t="s">
         <v>200</v>
@@ -14055,7 +14044,7 @@
         <v>92</v>
       </c>
       <c r="D581" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="E581" s="3" t="s">
         <v>483</v>
@@ -14075,7 +14064,7 @@
         <v>92</v>
       </c>
       <c r="D582" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>111</v>
@@ -14095,7 +14084,7 @@
         <v>92</v>
       </c>
       <c r="D583" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E583" s="3" t="s">
         <v>483</v>
@@ -14115,7 +14104,7 @@
         <v>92</v>
       </c>
       <c r="D584" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E584" s="3" t="s">
         <v>483</v>
@@ -14135,7 +14124,7 @@
         <v>92</v>
       </c>
       <c r="D585" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E585" t="s">
         <v>200</v>
@@ -14152,7 +14141,7 @@
         <v>92</v>
       </c>
       <c r="D586" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E586" t="s">
         <v>200</v>
@@ -14169,7 +14158,7 @@
         <v>92</v>
       </c>
       <c r="D587" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E587" s="3" t="s">
         <v>483</v>
@@ -14189,7 +14178,7 @@
         <v>92</v>
       </c>
       <c r="D588" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E588" s="3" t="s">
         <v>483</v>
@@ -14209,7 +14198,7 @@
         <v>92</v>
       </c>
       <c r="D589" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E589" s="3" t="s">
         <v>483</v>
@@ -14229,7 +14218,7 @@
         <v>92</v>
       </c>
       <c r="D590" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="E590" s="3" t="s">
         <v>483</v>
@@ -14755,7 +14744,7 @@
         <v>92</v>
       </c>
       <c r="D619" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E619" s="3" t="s">
         <v>483</v>
@@ -14775,7 +14764,7 @@
         <v>92</v>
       </c>
       <c r="D620" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E620" s="3" t="s">
         <v>483</v>
@@ -14795,7 +14784,7 @@
         <v>92</v>
       </c>
       <c r="D621" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E621" t="s">
         <v>200</v>
@@ -14812,7 +14801,7 @@
         <v>92</v>
       </c>
       <c r="D622" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="E622" s="3" t="s">
         <v>483</v>
@@ -14832,7 +14821,7 @@
         <v>92</v>
       </c>
       <c r="D623" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E623" s="1" t="s">
         <v>111</v>
@@ -14852,7 +14841,7 @@
         <v>92</v>
       </c>
       <c r="D624" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E624" t="s">
         <v>159</v>
@@ -14869,7 +14858,7 @@
         <v>92</v>
       </c>
       <c r="D625" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E625" s="3" t="s">
         <v>483</v>
@@ -14889,7 +14878,7 @@
         <v>92</v>
       </c>
       <c r="D626" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="E626" s="3" t="s">
         <v>483</v>
@@ -14909,7 +14898,7 @@
         <v>92</v>
       </c>
       <c r="D627" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E627" t="s">
         <v>200</v>
@@ -14926,7 +14915,7 @@
         <v>92</v>
       </c>
       <c r="D628" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E628" s="3" t="s">
         <v>483</v>
@@ -14946,7 +14935,7 @@
         <v>92</v>
       </c>
       <c r="D629" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E629" s="3" t="s">
         <v>483</v>
@@ -14966,7 +14955,7 @@
         <v>92</v>
       </c>
       <c r="D630" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E630" s="3" t="s">
         <v>483</v>
@@ -14986,7 +14975,7 @@
         <v>92</v>
       </c>
       <c r="D631" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="E631" s="3" t="s">
         <v>483</v>
@@ -15006,7 +14995,7 @@
         <v>92</v>
       </c>
       <c r="D632" s="3" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E632" s="3" t="s">
         <v>483</v>
@@ -15026,7 +15015,7 @@
         <v>92</v>
       </c>
       <c r="D633" s="3" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E633" s="3" t="s">
         <v>483</v>
@@ -15046,7 +15035,7 @@
         <v>92</v>
       </c>
       <c r="D634" s="3" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="E634" t="s">
         <v>200</v>
@@ -15063,7 +15052,7 @@
         <v>92</v>
       </c>
       <c r="D635" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E635" t="s">
         <v>159</v>
@@ -15080,7 +15069,7 @@
         <v>92</v>
       </c>
       <c r="D636" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E636" s="3" t="s">
         <v>483</v>
@@ -15100,7 +15089,7 @@
         <v>92</v>
       </c>
       <c r="D637" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E637" s="3" t="s">
         <v>483</v>
@@ -15120,7 +15109,7 @@
         <v>92</v>
       </c>
       <c r="D638" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="E638" s="3" t="s">
         <v>483</v>
@@ -15140,7 +15129,7 @@
         <v>92</v>
       </c>
       <c r="D639" s="3" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E639" s="3" t="s">
         <v>483</v>
@@ -15160,7 +15149,7 @@
         <v>92</v>
       </c>
       <c r="D640" s="3" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E640" s="3" t="s">
         <v>483</v>
@@ -15180,7 +15169,7 @@
         <v>92</v>
       </c>
       <c r="D641" s="3" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="E641" t="s">
         <v>159</v>
@@ -15197,7 +15186,7 @@
         <v>92</v>
       </c>
       <c r="D642" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E642" s="3" t="s">
         <v>483</v>
@@ -15217,7 +15206,7 @@
         <v>92</v>
       </c>
       <c r="D643" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E643" t="s">
         <v>200</v>
@@ -15234,7 +15223,7 @@
         <v>92</v>
       </c>
       <c r="D644" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E644" s="3" t="s">
         <v>483</v>
@@ -15254,7 +15243,7 @@
         <v>92</v>
       </c>
       <c r="D645" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="E645" s="3" t="s">
         <v>483</v>
@@ -20585,7 +20574,7 @@
       <c r="C932" t="s">
         <v>199</v>
       </c>
-      <c r="D932" t="s">
+      <c r="D932" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E932" s="1" t="s">
@@ -20605,7 +20594,7 @@
       <c r="C933" t="s">
         <v>199</v>
       </c>
-      <c r="D933" t="s">
+      <c r="D933" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E933" t="s">
@@ -20622,7 +20611,7 @@
       <c r="C934" t="s">
         <v>199</v>
       </c>
-      <c r="D934" t="s">
+      <c r="D934" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E934" t="s">
@@ -20642,7 +20631,7 @@
       <c r="C935" t="s">
         <v>199</v>
       </c>
-      <c r="D935" t="s">
+      <c r="D935" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E935" s="3" t="s">
@@ -20662,7 +20651,7 @@
       <c r="C936" t="s">
         <v>199</v>
       </c>
-      <c r="D936" t="s">
+      <c r="D936" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E936" t="s">
@@ -20682,7 +20671,7 @@
       <c r="C937" t="s">
         <v>199</v>
       </c>
-      <c r="D937" t="s">
+      <c r="D937" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E937" t="s">
@@ -20699,7 +20688,7 @@
       <c r="C938" t="s">
         <v>199</v>
       </c>
-      <c r="D938" t="s">
+      <c r="D938" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E938" t="s">
@@ -20716,7 +20705,7 @@
       <c r="C939" t="s">
         <v>199</v>
       </c>
-      <c r="D939" t="s">
+      <c r="D939" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E939" t="s">
@@ -20733,7 +20722,7 @@
       <c r="C940" t="s">
         <v>199</v>
       </c>
-      <c r="D940" t="s">
+      <c r="D940" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E940" t="s">
@@ -20753,7 +20742,7 @@
       <c r="C941" t="s">
         <v>199</v>
       </c>
-      <c r="D941" t="s">
+      <c r="D941" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E941" t="s">
@@ -20773,7 +20762,7 @@
       <c r="C942" t="s">
         <v>199</v>
       </c>
-      <c r="D942" t="s">
+      <c r="D942" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E942" t="s">
@@ -20790,7 +20779,7 @@
       <c r="C943" t="s">
         <v>199</v>
       </c>
-      <c r="D943" t="s">
+      <c r="D943" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E943" t="s">
@@ -20807,7 +20796,7 @@
       <c r="C944" t="s">
         <v>199</v>
       </c>
-      <c r="D944" t="s">
+      <c r="D944" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E944" s="3" t="s">
@@ -20827,7 +20816,7 @@
       <c r="C945" t="s">
         <v>199</v>
       </c>
-      <c r="D945" t="s">
+      <c r="D945" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E945" t="s">
@@ -20847,7 +20836,7 @@
       <c r="C946" t="s">
         <v>199</v>
       </c>
-      <c r="D946" t="s">
+      <c r="D946" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E946" t="s">
@@ -20864,7 +20853,7 @@
       <c r="C947" t="s">
         <v>199</v>
       </c>
-      <c r="D947" t="s">
+      <c r="D947" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E947" t="s">
@@ -20884,7 +20873,7 @@
       <c r="C948" t="s">
         <v>199</v>
       </c>
-      <c r="D948" t="s">
+      <c r="D948" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E948" t="s">
@@ -20901,7 +20890,7 @@
       <c r="C949" t="s">
         <v>199</v>
       </c>
-      <c r="D949" t="s">
+      <c r="D949" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E949" t="s">
@@ -20918,7 +20907,7 @@
       <c r="C950" t="s">
         <v>199</v>
       </c>
-      <c r="D950" t="s">
+      <c r="D950" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E950" t="s">
@@ -20935,7 +20924,7 @@
       <c r="C951" t="s">
         <v>199</v>
       </c>
-      <c r="D951" t="s">
+      <c r="D951" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E951" t="s">
@@ -20952,7 +20941,7 @@
       <c r="C952" t="s">
         <v>199</v>
       </c>
-      <c r="D952" t="s">
+      <c r="D952" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E952" t="s">
@@ -20969,7 +20958,7 @@
       <c r="C953" t="s">
         <v>199</v>
       </c>
-      <c r="D953" t="s">
+      <c r="D953" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E953" t="s">
@@ -20986,7 +20975,7 @@
       <c r="C954" t="s">
         <v>199</v>
       </c>
-      <c r="D954" t="s">
+      <c r="D954" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E954" t="s">
@@ -21003,7 +20992,7 @@
       <c r="C955" t="s">
         <v>199</v>
       </c>
-      <c r="D955" t="s">
+      <c r="D955" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E955" t="s">
@@ -21020,7 +21009,7 @@
       <c r="C956" t="s">
         <v>199</v>
       </c>
-      <c r="D956" t="s">
+      <c r="D956" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E956" t="s">
@@ -21037,7 +21026,7 @@
       <c r="C957" t="s">
         <v>199</v>
       </c>
-      <c r="D957" t="s">
+      <c r="D957" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E957" s="3" t="s">
@@ -21057,7 +21046,7 @@
       <c r="C958" t="s">
         <v>199</v>
       </c>
-      <c r="D958" t="s">
+      <c r="D958" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E958" t="s">
@@ -21074,7 +21063,7 @@
       <c r="C959" t="s">
         <v>199</v>
       </c>
-      <c r="D959" t="s">
+      <c r="D959" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E959" t="s">
@@ -21091,7 +21080,7 @@
       <c r="C960" t="s">
         <v>199</v>
       </c>
-      <c r="D960" t="s">
+      <c r="D960" s="1" t="s">
         <v>226</v>
       </c>
       <c r="E960" t="s">
@@ -21108,8 +21097,8 @@
       <c r="C961" t="s">
         <v>199</v>
       </c>
-      <c r="D961" t="s">
-        <v>897</v>
+      <c r="D961" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="E961" t="s">
         <v>118</v>
@@ -21209,7 +21198,7 @@
         <v>91</v>
       </c>
       <c r="F966" s="3" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="967" spans="1:7" x14ac:dyDescent="0.4">
@@ -21269,7 +21258,7 @@
         <v>91</v>
       </c>
       <c r="F969" s="3" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="970" spans="1:7" x14ac:dyDescent="0.4">
@@ -21607,7 +21596,7 @@
         <v>199</v>
       </c>
       <c r="D988" t="s">
-        <v>896</v>
+        <v>235</v>
       </c>
       <c r="E988" s="3" t="s">
         <v>483</v>
@@ -21627,13 +21616,13 @@
         <v>199</v>
       </c>
       <c r="D989" t="s">
-        <v>896</v>
+        <v>235</v>
       </c>
       <c r="E989" t="s">
         <v>91</v>
       </c>
       <c r="F989" s="3" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.4">
@@ -21847,7 +21836,7 @@
         <v>91</v>
       </c>
       <c r="F1000" s="3" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.4">
